--- a/客户关系清单.xlsx
+++ b/客户关系清单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12041\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12041\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8748DA1C-BC82-476B-A6AB-4947E9111F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D05975-9226-4A43-8A6A-414601EFC12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="20715" windowHeight="13275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总" sheetId="1" r:id="rId1"/>
@@ -22,25 +22,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">外部!$A$1:$B$2752</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">总!$A$1:$B$2818</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10906" uniqueCount="3854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10988" uniqueCount="3858">
   <si>
     <t>客户名称</t>
   </si>
@@ -11602,13 +11589,27 @@
   </si>
   <si>
     <t>现代牧业(曲靖)有限公司</t>
+  </si>
+  <si>
+    <t>贵港海龙生物科技有限公司</t>
+  </si>
+  <si>
+    <t>佛山市得宝生物集团有限公司佛山分公司</t>
+  </si>
+  <si>
+    <t>海大集团</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>双胞胎集团</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11680,6 +11681,20 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -11719,7 +11734,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -11739,6 +11754,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF74AFE1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -11772,7 +11802,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -11843,6 +11873,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -14695,7 +14734,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B2818"/>
+  <dimension ref="A1:B2859"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="47.1328125" style="4" customWidth="1"/>
@@ -32319,6 +32358,334 @@
       </c>
       <c r="B2818" s="4" t="s">
         <v>533</v>
+      </c>
+    </row>
+    <row r="2819" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2819" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2819" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2820" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2820" s="24" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B2820" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2821" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2821" s="24" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B2821" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2822" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2822" s="24" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B2822" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2823" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2823" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2823" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2824" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2824" s="24" t="s">
+        <v>3854</v>
+      </c>
+      <c r="B2824" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2825" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2825" s="24" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B2825" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2826" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2826" s="24" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B2826" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2827" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2827" s="24" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B2827" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2828" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2828" s="24" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B2828" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2829" s="24" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B2829" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2830" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2830" s="24" t="s">
+        <v>2992</v>
+      </c>
+      <c r="B2830" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2831" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2831" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2831" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2832" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2832" s="24" t="s">
+        <v>2990</v>
+      </c>
+      <c r="B2832" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2833" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2833" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2833" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2834" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2834" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2835" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2835" s="24" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B2835" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2836" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2836" s="24" t="s">
+        <v>3855</v>
+      </c>
+      <c r="B2836" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2837" s="24" t="s">
+        <v>3334</v>
+      </c>
+      <c r="B2837" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2838" s="24" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B2838" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2839" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2839" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2839" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2840" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2840" s="24" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B2840" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2841" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2841" s="24" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B2841" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2842" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2842" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2842" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2843" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2843" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2843" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2844" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2844" s="24" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B2844" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2845" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2845" s="24" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B2845" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2846" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2846" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2846" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2847" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2847" s="24" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B2847" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2848" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2848" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2848" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2849" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2849" s="24" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B2849" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2850" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2850" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2850" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2851" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2851" s="24" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B2851" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2852" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2852" s="24" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B2852" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2853" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2853" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2853" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2854" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2854" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2854" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2855" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2855" s="24" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B2855" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2856" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2856" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2856" s="25" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="2857" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2857" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="B2857" s="25" t="s">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="2858" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2858" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B2858" s="25" t="s">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="2859" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2859" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2859" s="25" t="s">
+        <v>3857</v>
       </c>
     </row>
   </sheetData>
@@ -57295,13 +57662,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C262"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44.19921875" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.1328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -57309,7 +57676,7 @@
         <v>3805</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -57317,7 +57684,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -57325,7 +57692,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -57333,7 +57700,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -57341,7 +57708,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -57349,7 +57716,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -57357,7 +57724,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
@@ -57365,7 +57732,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -57373,7 +57740,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -57381,7 +57748,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -57389,7 +57756,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -57397,7 +57764,7 @@
         <v>3807</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
@@ -57405,7 +57772,7 @@
         <v>3807</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
@@ -57413,7 +57780,7 @@
         <v>3807</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>16</v>
       </c>
@@ -57421,7 +57788,7 @@
         <v>3807</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
@@ -57429,7 +57796,7 @@
         <v>3808</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
@@ -57437,7 +57804,7 @@
         <v>3809</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>19</v>
       </c>
@@ -57445,7 +57812,7 @@
         <v>3809</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>20</v>
       </c>
@@ -57453,7 +57820,7 @@
         <v>3809</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>21</v>
       </c>
@@ -57461,7 +57828,7 @@
         <v>3809</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>22</v>
       </c>
@@ -57469,7 +57836,7 @@
         <v>3809</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>23</v>
       </c>
@@ -57477,7 +57844,7 @@
         <v>3809</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>24</v>
       </c>
@@ -57485,7 +57852,7 @@
         <v>3809</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>25</v>
       </c>
@@ -57493,7 +57860,7 @@
         <v>3810</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>26</v>
       </c>
@@ -57501,7 +57868,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>27</v>
       </c>
@@ -57509,7 +57876,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>28</v>
       </c>
@@ -57517,7 +57884,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>29</v>
       </c>
@@ -57525,7 +57892,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>30</v>
       </c>
@@ -57533,7 +57900,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>31</v>
       </c>
@@ -57541,7 +57908,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>32</v>
       </c>
@@ -57549,7 +57916,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>33</v>
       </c>
@@ -57557,7 +57924,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>34</v>
       </c>
@@ -57565,7 +57932,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>35</v>
       </c>
@@ -57573,7 +57940,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>36</v>
       </c>
@@ -57581,7 +57948,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>37</v>
       </c>
@@ -57589,7 +57956,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>38</v>
       </c>
@@ -57597,7 +57964,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>39</v>
       </c>
@@ -57605,7 +57972,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>40</v>
       </c>
@@ -57613,7 +57980,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>41</v>
       </c>
@@ -57621,7 +57988,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>42</v>
       </c>
@@ -57629,7 +57996,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>43</v>
       </c>
@@ -57637,7 +58004,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>44</v>
       </c>
@@ -57645,7 +58012,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>45</v>
       </c>
@@ -57653,7 +58020,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>46</v>
       </c>
@@ -57661,7 +58028,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>50</v>
       </c>
@@ -57669,7 +58036,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>59</v>
       </c>
@@ -57677,7 +58044,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>60</v>
       </c>
@@ -57685,7 +58052,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>61</v>
       </c>
@@ -57693,7 +58060,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>62</v>
       </c>
@@ -57701,7 +58068,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>63</v>
       </c>
@@ -57709,7 +58076,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>64</v>
       </c>
@@ -57717,7 +58084,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>65</v>
       </c>
@@ -57725,7 +58092,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>66</v>
       </c>
@@ -57733,7 +58100,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>67</v>
       </c>
@@ -57741,7 +58108,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>68</v>
       </c>
@@ -57749,7 +58116,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>69</v>
       </c>
@@ -57757,7 +58124,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>70</v>
       </c>
@@ -57765,7 +58132,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>71</v>
       </c>
@@ -57773,7 +58140,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>72</v>
       </c>
@@ -57781,7 +58148,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>73</v>
       </c>
@@ -57789,7 +58156,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>74</v>
       </c>
@@ -57797,7 +58164,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>75</v>
       </c>
@@ -57805,7 +58172,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>76</v>
       </c>
@@ -57813,7 +58180,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>77</v>
       </c>
@@ -57821,7 +58188,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>78</v>
       </c>
@@ -57829,7 +58196,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>79</v>
       </c>
@@ -57837,7 +58204,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>80</v>
       </c>
@@ -57845,7 +58212,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>81</v>
       </c>
@@ -57853,7 +58220,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>82</v>
       </c>
@@ -57861,7 +58228,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>83</v>
       </c>
@@ -57869,7 +58236,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>84</v>
       </c>
@@ -57877,7 +58244,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>85</v>
       </c>
@@ -57885,7 +58252,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>86</v>
       </c>
@@ -57893,7 +58260,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>87</v>
       </c>
@@ -57901,7 +58268,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>89</v>
       </c>
@@ -57909,7 +58276,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>90</v>
       </c>
@@ -57917,7 +58284,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>91</v>
       </c>
@@ -57925,7 +58292,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>92</v>
       </c>
@@ -57933,7 +58300,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>93</v>
       </c>
@@ -57941,7 +58308,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>94</v>
       </c>
@@ -57949,7 +58316,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>95</v>
       </c>
@@ -57957,7 +58324,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>96</v>
       </c>
@@ -57965,7 +58332,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>97</v>
       </c>
@@ -57973,7 +58340,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>98</v>
       </c>
@@ -57981,7 +58348,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>99</v>
       </c>
@@ -57989,7 +58356,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>100</v>
       </c>
@@ -57997,7 +58364,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>101</v>
       </c>
@@ -58005,7 +58372,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>102</v>
       </c>
@@ -58013,7 +58380,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>103</v>
       </c>
@@ -58021,7 +58388,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>104</v>
       </c>
@@ -58029,7 +58396,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>106</v>
       </c>
@@ -58037,7 +58404,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>107</v>
       </c>
@@ -58045,7 +58412,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>108</v>
       </c>
@@ -58053,7 +58420,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>109</v>
       </c>
@@ -58061,7 +58428,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>110</v>
       </c>
@@ -58069,7 +58436,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>111</v>
       </c>
@@ -58077,7 +58444,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>112</v>
       </c>
@@ -58085,7 +58452,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>113</v>
       </c>
@@ -58093,7 +58460,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>114</v>
       </c>
@@ -58101,7 +58468,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>115</v>
       </c>
@@ -58109,7 +58476,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>116</v>
       </c>
@@ -58117,7 +58484,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>117</v>
       </c>
@@ -58125,7 +58492,7 @@
         <v>3815</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>118</v>
       </c>
@@ -58133,7 +58500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>1059</v>
       </c>
@@ -58141,7 +58508,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>1078</v>
       </c>
@@ -58149,7 +58516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>1086</v>
       </c>
@@ -58157,7 +58524,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>1152</v>
       </c>
@@ -58165,7 +58532,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>1172</v>
       </c>
@@ -58173,7 +58540,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>1176</v>
       </c>
@@ -58181,7 +58548,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>1182</v>
       </c>
@@ -58189,7 +58556,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>1199</v>
       </c>
@@ -58197,7 +58564,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>1201</v>
       </c>
@@ -58205,7 +58572,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>88</v>
       </c>
@@ -58213,7 +58580,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>1521</v>
       </c>
@@ -58221,7 +58588,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>1537</v>
       </c>
@@ -58229,7 +58596,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>1571</v>
       </c>
@@ -58237,7 +58604,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>1578</v>
       </c>
@@ -58245,7 +58612,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>1636</v>
       </c>
@@ -58253,7 +58620,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>1677</v>
       </c>
@@ -58261,7 +58628,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>1686</v>
       </c>
@@ -58269,7 +58636,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
         <v>1688</v>
       </c>
@@ -58277,7 +58644,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
         <v>1698</v>
       </c>
@@ -58285,7 +58652,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A124" s="7" t="s">
         <v>1717</v>
       </c>
@@ -58293,7 +58660,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A125" s="7" t="s">
         <v>1737</v>
       </c>
@@ -58301,7 +58668,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>1743</v>
       </c>
@@ -58309,7 +58676,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A127" s="7" t="s">
         <v>1767</v>
       </c>
@@ -58317,7 +58684,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>1770</v>
       </c>
@@ -58325,7 +58692,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>1771</v>
       </c>
@@ -58333,7 +58700,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>1773</v>
       </c>
@@ -58341,7 +58708,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>1778</v>
       </c>
@@ -58349,7 +58716,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>1779</v>
       </c>
@@ -58357,7 +58724,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>1780</v>
       </c>
@@ -58365,7 +58732,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>1782</v>
       </c>
@@ -58373,7 +58740,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>1785</v>
       </c>
@@ -58381,7 +58748,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>1787</v>
       </c>
@@ -58389,7 +58756,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>1789</v>
       </c>
@@ -58397,7 +58764,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>1792</v>
       </c>
@@ -58405,7 +58772,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>1801</v>
       </c>
@@ -58413,7 +58780,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>1813</v>
       </c>
@@ -58421,7 +58788,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
         <v>1825</v>
       </c>
@@ -58429,7 +58796,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A142" s="9" t="s">
         <v>1829</v>
       </c>
@@ -58437,7 +58804,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A143" s="9" t="s">
         <v>1849</v>
       </c>
@@ -58445,7 +58812,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
         <v>1866</v>
       </c>
@@ -58453,7 +58820,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A145" s="9" t="s">
         <v>1872</v>
       </c>
@@ -58461,7 +58828,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
         <v>1887</v>
       </c>
@@ -58469,7 +58836,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A147" s="9" t="s">
         <v>1915</v>
       </c>
@@ -58477,7 +58844,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A148" s="9" t="s">
         <v>1945</v>
       </c>
@@ -58485,7 +58852,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A149" s="9" t="s">
         <v>1956</v>
       </c>
@@ -58493,7 +58860,7 @@
         <v>3813</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
         <v>2012</v>
       </c>
@@ -58501,7 +58868,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A151" s="9" t="s">
         <v>2051</v>
       </c>
@@ -58509,7 +58876,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A152" s="9" t="s">
         <v>2090</v>
       </c>
@@ -58517,7 +58884,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A153" s="9" t="s">
         <v>2096</v>
       </c>
@@ -58525,7 +58892,7 @@
         <v>3812</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A154" s="9" t="s">
         <v>2153</v>
       </c>
@@ -58533,7 +58900,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A155" s="9" t="s">
         <v>2155</v>
       </c>
@@ -58541,7 +58908,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A156" s="9" t="s">
         <v>105</v>
       </c>
@@ -58549,7 +58916,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A157" s="9" t="s">
         <v>2159</v>
       </c>
@@ -58557,7 +58924,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A158" s="9" t="s">
         <v>2160</v>
       </c>
@@ -58565,7 +58932,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A159" s="9" t="s">
         <v>2161</v>
       </c>
@@ -58573,7 +58940,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" ht="15" x14ac:dyDescent="0.3">
       <c r="A160" s="9" t="s">
         <v>2162</v>
       </c>
@@ -58581,7 +58948,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A161" s="9" t="s">
         <v>2163</v>
       </c>
@@ -58589,7 +58956,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
         <v>2164</v>
       </c>
@@ -58597,7 +58964,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="s">
         <v>2165</v>
       </c>
@@ -58605,7 +58972,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
         <v>2166</v>
       </c>
@@ -58613,7 +58980,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A165" s="9" t="s">
         <v>2167</v>
       </c>
@@ -58621,7 +58988,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A166" s="9" t="s">
         <v>2168</v>
       </c>
@@ -58629,7 +58996,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A167" s="9" t="s">
         <v>2169</v>
       </c>
@@ -58637,7 +59004,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A168" s="9" t="s">
         <v>2170</v>
       </c>
@@ -58645,7 +59012,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="s">
         <v>3816</v>
       </c>
@@ -58656,7 +59023,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A170" s="9" t="s">
         <v>3818</v>
       </c>
@@ -58667,7 +59034,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A171" s="9" t="s">
         <v>3819</v>
       </c>
@@ -58678,7 +59045,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A172" s="9" t="s">
         <v>3820</v>
       </c>
@@ -58689,7 +59056,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A173" s="9" t="s">
         <v>3822</v>
       </c>
@@ -58700,7 +59067,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A174" s="9" t="s">
         <v>3824</v>
       </c>
@@ -58711,7 +59078,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A175" s="9" t="s">
         <v>3825</v>
       </c>
@@ -58722,7 +59089,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A176" s="9" t="s">
         <v>3826</v>
       </c>
@@ -58733,7 +59100,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A177" s="9" t="s">
         <v>3827</v>
       </c>
@@ -58744,7 +59111,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A178" s="9" t="s">
         <v>3828</v>
       </c>
@@ -58755,7 +59122,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A179" s="9" t="s">
         <v>3829</v>
       </c>
@@ -58766,7 +59133,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A180" s="9" t="s">
         <v>3830</v>
       </c>
@@ -58777,7 +59144,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A181" s="9" t="s">
         <v>3831</v>
       </c>
@@ -58788,7 +59155,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A182" s="9" t="s">
         <v>3832</v>
       </c>
@@ -58799,7 +59166,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A183" s="9" t="s">
         <v>3833</v>
       </c>
@@ -58810,7 +59177,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A184" s="9" t="s">
         <v>3834</v>
       </c>
@@ -58821,7 +59188,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A185" s="9" t="s">
         <v>3835</v>
       </c>
@@ -58832,7 +59199,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A186" s="9" t="s">
         <v>3836</v>
       </c>
@@ -58843,7 +59210,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A187" s="9" t="s">
         <v>3837</v>
       </c>
@@ -58854,7 +59221,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A188" s="9" t="s">
         <v>3838</v>
       </c>
@@ -58865,7 +59232,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A189" s="9" t="s">
         <v>3839</v>
       </c>
@@ -58876,7 +59243,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A190" s="9" t="s">
         <v>3840</v>
       </c>
@@ -58887,7 +59254,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A191" s="9" t="s">
         <v>3841</v>
       </c>
@@ -58898,7 +59265,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A192" s="9" t="s">
         <v>3842</v>
       </c>
@@ -58909,7 +59276,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A193" s="9" t="s">
         <v>3843</v>
       </c>
@@ -58920,7 +59287,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A194" s="9" t="s">
         <v>3844</v>
       </c>
@@ -58931,7 +59298,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A195" s="9" t="s">
         <v>3845</v>
       </c>
@@ -58942,7 +59309,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A196" s="9" t="s">
         <v>3846</v>
       </c>
@@ -58953,7 +59320,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A197" s="9" t="s">
         <v>3847</v>
       </c>
@@ -58964,7 +59331,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A198" s="9" t="s">
         <v>3848</v>
       </c>
@@ -58975,7 +59342,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A199" s="9" t="s">
         <v>3849</v>
       </c>
@@ -58986,7 +59353,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A200" s="9" t="s">
         <v>3850</v>
       </c>
@@ -58997,7 +59364,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A201" s="9" t="s">
         <v>3851</v>
       </c>
@@ -59008,7 +59375,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A202" s="9" t="s">
         <v>3852</v>
       </c>
@@ -59019,7 +59386,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A203" s="9" t="s">
         <v>3853</v>
       </c>
@@ -59030,7 +59397,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A204" s="9"/>
       <c r="B204" s="9"/>
       <c r="C204" s="10"/>
